--- a/utils/equity_tickers_lists.xlsx
+++ b/utils/equity_tickers_lists.xlsx
@@ -1343,12 +1343,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Application Software</t>
+          <t>Advertising</t>
         </is>
       </c>
     </row>
@@ -1619,144 +1619,144 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AVB</t>
+          <t>AVY</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AvalonBay Communities</t>
+          <t>Avery Dennison</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Multi-Family Residential REITs</t>
+          <t>Paper &amp; Plastic Packaging Products &amp; Materials</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AVY</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Avery Dennison</t>
+          <t>Axon Enterprise</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Paper &amp; Plastic Packaging Products &amp; Materials</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>BKR</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Axon Enterprise</t>
+          <t>Baker Hughes</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Oil &amp; Gas Equipment &amp; Services</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BKR</t>
+          <t>BALL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Baker Hughes</t>
+          <t>Ball Corporation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Equipment &amp; Services</t>
+          <t>Metal, Glass &amp; Plastic Containers</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BALL</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ball Corporation</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Metal, Glass &amp; Plastic Containers</t>
+          <t>Diversified Banks</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>BAX</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Baxter International</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Diversified Banks</t>
+          <t>Health Care Equipment</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BAX</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Baxter International</t>
+          <t>Becton Dickinson</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1773,78 +1773,78 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>BRK.B</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Becton Dickinson</t>
+          <t>Berkshire Hathaway</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Health Care Equipment</t>
+          <t>Multi-Sector Holdings</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BRK.B</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway</t>
+          <t>Best Buy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Multi-Sector Holdings</t>
+          <t>Computer &amp; Electronics Retail</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>Bio-Techne</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Computer &amp; Electronics Retail</t>
+          <t>Life Sciences Tools &amp; Services</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bio-Techne</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1854,41 +1854,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Life Sciences Tools &amp; Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Asset Management &amp; Custody Banks</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Blackstone Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1905,12 +1905,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Blackstone Inc.</t>
+          <t>Block, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1920,36 +1920,36 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Asset Management &amp; Custody Banks</t>
+          <t>Transaction &amp; Payment Processing Services</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Block, Inc.</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Transaction &amp; Payment Processing Services</t>
+          <t>Electrical Components &amp; Equipment</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BK</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2147,210 +2147,210 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BLDR</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Bunge Global</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Building Products</t>
+          <t>Agricultural Products &amp; Services</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>BXP</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bunge Global</t>
+          <t>BXP, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Agricultural Products &amp; Services</t>
+          <t>Office REITs</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BXP</t>
+          <t>CHRW</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BXP, Inc.</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Office REITs</t>
+          <t>Air Freight &amp; Logistics</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CHRW</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Cadence Design Systems</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Air Freight &amp; Logistics</t>
+          <t>Application Software</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>CPT</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cadence Design Systems</t>
+          <t>Camden Property Trust</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Application Software</t>
+          <t>Multi-Family Residential REITs</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CPT</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Camden Property Trust</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Multi-Family Residential REITs</t>
+          <t>Consumer Finance</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CPB</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Campbell's Company (The)</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Packaged Foods &amp; Meats</t>
+          <t>Health Care Distributors</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Carnival Corporation</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Consumer Finance</t>
+          <t>Hotels, Resorts &amp; Cruise Lines</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>CARR</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Carrier Global</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Health Care Distributors</t>
+          <t>Building Products</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Carnival</t>
+          <t>Carvana</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2360,151 +2360,151 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Hotels, Resorts &amp; Cruise Lines</t>
+          <t>Automotive Retail</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CARR</t>
+          <t>CASY</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Carrier Global</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Building Products</t>
+          <t>Food Retail</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Carvana</t>
+          <t>Caterpillar Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Automotive Retail</t>
+          <t>Construction Machinery &amp; Heavy Transportation Equipment</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>CBOE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Caterpillar Inc.</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Construction Machinery &amp; Heavy Transportation Equipment</t>
+          <t>Financial Exchanges &amp; Data</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CBOE</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>CBRE Group</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Financial Exchanges &amp; Data</t>
+          <t>Real Estate Services</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CBRE Group</t>
+          <t>CDW Corporation</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Real Estate Services</t>
+          <t>Technology Distributors</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CDW Corporation</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Technology Distributors</t>
+          <t>Health Care Distributors</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2514,349 +2514,349 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Health Care Distributors</t>
+          <t>Managed Health Care</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Centene Corporation</t>
+          <t>CenterPoint Energy</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Managed Health Care</t>
+          <t>Multi-Utilities</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CenterPoint Energy</t>
+          <t>CF Industries</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Multi-Utilities</t>
+          <t>Fertilizers &amp; Agricultural Chemicals</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>CRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CF Industries</t>
+          <t>Charles River Laboratories</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Fertilizers &amp; Agricultural Chemicals</t>
+          <t>Life Sciences Tools &amp; Services</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CRL</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Charles River Laboratories</t>
+          <t>Charles Schwab Corporation</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Life Sciences Tools &amp; Services</t>
+          <t>Investment Banking &amp; Brokerage</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Charles Schwab Corporation</t>
+          <t>Charter Communications</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Investment Banking &amp; Brokerage</t>
+          <t>Cable &amp; Satellite</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Charter Communications</t>
+          <t>Chevron Corporation</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Cable &amp; Satellite</t>
+          <t>Integrated Oil &amp; Gas</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Integrated Oil &amp; Gas</t>
+          <t>Restaurants</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Restaurants</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Church &amp; Dwight</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Household Products</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CHD</t>
+          <t>CIEN</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight</t>
+          <t>Ciena</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Household Products</t>
+          <t>Communications Equipment</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CIEN</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ciena</t>
+          <t>Cigna</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Communications Equipment</t>
+          <t>Health Care Services</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cigna</t>
+          <t>Cincinnati Financial</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cincinnati Financial</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Diversified Support Services</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Diversified Support Services</t>
+          <t>Communications Equipment</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Communications Equipment</t>
+          <t>Diversified Banks</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CFG</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>Citizens Financial Group</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2866,129 +2866,129 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Diversified Banks</t>
+          <t>Regional Banks</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CFG</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Citizens Financial Group</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Household Products</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Household Products</t>
+          <t>Financial Exchanges &amp; Data</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>CMS</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>CMS Energy</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Financial Exchanges &amp; Data</t>
+          <t>Multi-Utilities</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CMS</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CMS Energy</t>
+          <t>Coca-Cola Company (The)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Multi-Utilities</t>
+          <t>Soft Drinks &amp; Non-alcoholic Beverages</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Coca-Cola Company (The)</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Soft Drinks &amp; Non-alcoholic Beverages</t>
+          <t>IT Consulting &amp; Other Services</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Coherent Corp.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>IT Consulting &amp; Other Services</t>
+          <t>Electronic Components</t>
         </is>
       </c>
     </row>
@@ -3093,540 +3093,540 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CAG</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Conagra Brands</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Packaged Foods &amp; Meats</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Consolidated Edison</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Multi-Utilities</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>STZ</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Consolidated Edison</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Multi-Utilities</t>
+          <t>Distillers &amp; Vintners</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STZ</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Distillers &amp; Vintners</t>
+          <t>Electric Utilities</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Cooper Companies (The)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Electric Utilities</t>
+          <t>Health Care Supplies</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Cooper Companies (The)</t>
+          <t>Copart</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Health Care Supplies</t>
+          <t>Diversified Support Services</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Copart</t>
+          <t>Corning Inc.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Diversified Support Services</t>
+          <t>Electronic Components</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Corning Inc.</t>
+          <t>Corpay</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Transaction &amp; Payment Processing Services</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>CTVA</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Corpay</t>
+          <t>Corteva</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Transaction &amp; Payment Processing Services</t>
+          <t>Fertilizers &amp; Agricultural Chemicals</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CTVA</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Corteva</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Fertilizers &amp; Agricultural Chemicals</t>
+          <t>Real Estate Services</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Costco</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Real Estate Services</t>
+          <t>Consumer Staples Merchandise Retail</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CRH</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Costco</t>
+          <t>CRH plc</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Consumer Staples Merchandise Retail</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CTRA</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Coterra</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Systems Software</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CRH</t>
+          <t>CCI</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CRH plc</t>
+          <t>Crown Castle</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Telecom Tower REITs</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>CSX Corporation</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Systems Software</t>
+          <t>Rail Transportation</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CCI</t>
+          <t>CMI</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Crown Castle</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Telecom Tower REITs</t>
+          <t>Construction Machinery &amp; Heavy Transportation Equipment</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CSX Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Rail Transportation</t>
+          <t>Health Care Services</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CMI</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Construction Machinery &amp; Heavy Transportation Equipment</t>
+          <t>Life Sciences Tools &amp; Services</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Darden Restaurants</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Restaurants</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Life Sciences Tools &amp; Services</t>
+          <t>Application Software</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>DVA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Darden Restaurants</t>
+          <t>DaVita</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Restaurants</t>
+          <t>Health Care Services</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>DECK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Deckers Brands</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Application Software</t>
+          <t>Footwear</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>DVA</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DaVita</t>
+          <t>Deere &amp; Company</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Agricultural &amp; Farm Machinery</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DECK</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Deckers Brands</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Technology Hardware, Storage &amp; Peripherals</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Deere &amp; Company</t>
+          <t>Delta Air Lines</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3636,63 +3636,63 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Agricultural &amp; Farm Machinery</t>
+          <t>Passenger Airlines</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Technology Hardware, Storage &amp; Peripherals</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Dexcom</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Passenger Airlines</t>
+          <t>Health Care Equipment</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Diamondback Energy</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3709,408 +3709,408 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Dexcom</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Health Care Equipment</t>
+          <t>Data Center REITs</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Diamondback Energy</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Consumer Staples Merchandise Retail</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Dollar Tree</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Data Center REITs</t>
+          <t>Consumer Staples Merchandise Retail</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Consumer Staples Merchandise Retail</t>
+          <t>Multi-Utilities</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>DPZ</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Dollar Tree</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Consumer Staples Merchandise Retail</t>
+          <t>Restaurants</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Multi-Utilities</t>
+          <t>Specialized Consumer Services</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>DPZ</t>
+          <t>DOV</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Dover Corporation</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Restaurants</t>
+          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Dow Inc.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Specialized Consumer Services</t>
+          <t>Commodity Chemicals</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>DOV</t>
+          <t>DHI</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Dover Corporation</t>
+          <t>D. R. Horton</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
+          <t>Homebuilding</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>DTE</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Dow Inc.</t>
+          <t>DTE Energy</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Commodity Chemicals</t>
+          <t>Multi-Utilities</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>DHI</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>D. R. Horton</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Homebuilding</t>
+          <t>Electric Utilities</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>DTE</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>DTE Energy</t>
+          <t>DuPont</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Multi-Utilities</t>
+          <t>Industrial Conglomerates</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Eaton Corporation</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Electric Utilities</t>
+          <t>Electrical Components &amp; Equipment</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DuPont</t>
+          <t>eBay Inc.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Specialty Chemicals</t>
+          <t>Broadline Retail</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>ECHO</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Eaton Corporation</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Electrical Components &amp; Equipment</t>
+          <t>Wireless Telecommunication Services</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>eBay Inc.</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Broadline Retail</t>
+          <t>Specialty Chemicals</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>EIX</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Edison International</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Specialty Chemicals</t>
+          <t>Electric Utilities</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Edison International</t>
+          <t>Edwards Lifesciences</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Electric Utilities</t>
+          <t>Health Care Equipment</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4120,591 +4120,591 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Health Care Equipment</t>
+          <t>Managed Health Care</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>EME</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Emcor</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Interactive Home Entertainment</t>
+          <t>Construction &amp; Engineering</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Managed Health Care</t>
+          <t>Electrical Components &amp; Equipment</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>EME</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Emcor</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Construction &amp; Engineering</t>
+          <t>Electric Utilities</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>EOG Resources</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Electrical Components &amp; Equipment</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>EQT</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>EQT Corporation</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Electric Utilities</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>EOG Resources</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Research &amp; Consulting Services</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>IT Consulting &amp; Other Services</t>
+          <t>Data Center REITs</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>EQT</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>EQT Corporation</t>
+          <t>Erie Indemnity</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Insurance Brokers</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>ESS</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Essex Property Trust</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Research &amp; Consulting Services</t>
+          <t>Multi-Family Residential REITs</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Estée Lauder Companies (The)</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Data Center REITs</t>
+          <t>Personal Care Products</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>EQR</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Equity Residential</t>
+          <t>Everest Group</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Multi-Family Residential REITs</t>
+          <t>Reinsurance</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Erie Indemnity</t>
+          <t>Evergy</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Insurance Brokers</t>
+          <t>Electric Utilities</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ESS</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Essex Property Trust</t>
+          <t>Everpure</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Multi-Family Residential REITs</t>
+          <t>Technology Hardware, Storage &amp; Peripherals</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Estée Lauder Companies (The)</t>
+          <t>Eversource Energy</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Personal Care Products</t>
+          <t>Electric Utilities</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Everest Group</t>
+          <t>Exelon</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Reinsurance</t>
+          <t>Electric Utilities</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Evergy</t>
+          <t>Expand Energy</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Electric Utilities</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Eversource Energy</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Electric Utilities</t>
+          <t>Hotels, Resorts &amp; Cruise Lines</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Exelon</t>
+          <t>Expeditors International</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Electric Utilities</t>
+          <t>Air Freight &amp; Logistics</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>EXR</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Expand Energy</t>
+          <t>Extra Space Storage</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Self-Storage REITs</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Hotels, Resorts &amp; Cruise Lines</t>
+          <t>Integrated Oil &amp; Gas</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Expeditors International</t>
+          <t>F5, Inc.</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Air Freight &amp; Logistics</t>
+          <t>Communications Equipment</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>EXR</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Extra Space Storage</t>
+          <t>FactSet</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Self-Storage REITs</t>
+          <t>Financial Exchanges &amp; Data</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Fair Isaac</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Integrated Oil &amp; Gas</t>
+          <t>Application Software</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>F5, Inc.</t>
+          <t>Fastenal</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Communications Equipment</t>
+          <t>Trading Companies &amp; Distributors</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>FRT</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>FactSet</t>
+          <t>Federal Realty Investment Trust</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Financial Exchanges &amp; Data</t>
+          <t>Retail REITs</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Fair Isaac</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Application Software</t>
+          <t>Air Freight &amp; Logistics</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>FDXF</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Fastenal</t>
+          <t>FedEx Freight</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4714,63 +4714,63 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Trading Companies &amp; Distributors</t>
+          <t>Cargo Ground Transportation</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>FRT</t>
+          <t>FERG</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Federal Realty Investment Trust</t>
+          <t>Ferguson Enterprises</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Retail REITs</t>
+          <t>Trading Companies &amp; Distributors</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>Fidelity National Information Services</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Air Freight &amp; Logistics</t>
+          <t>Transaction &amp; Payment Processing Services</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Fidelity National Information Services</t>
+          <t>Fifth Third Bancorp</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4780,95 +4780,95 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Transaction &amp; Payment Processing Services</t>
+          <t>Regional Banks</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp</t>
+          <t>First Solar</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>FE</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>First Solar</t>
+          <t>FirstEnergy</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Electric Utilities</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>FE</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>FirstEnergy</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Electric Utilities</t>
+          <t>Transaction &amp; Payment Processing Services</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Flex Ltd.</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Transaction &amp; Payment Processing Services</t>
+          <t>Electronic Manufacturing Services</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Electrical Components &amp; Equipment</t>
+          <t>Heavy Electrical Equipment</t>
         </is>
       </c>
     </row>
@@ -5579,44 +5579,44 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>HOLX</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Hologic</t>
+          <t>Home Depot (The)</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Health Care Equipment</t>
+          <t>Home Improvement Retail</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>HONA</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Home Depot (The)</t>
+          <t>Honeywell Aerospace</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Home Improvement Retail</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Honeywell Technologies</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5909,12 +5909,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Incyte</t>
+          <t>Illumina, Inc.</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5924,107 +5924,107 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Life Sciences Tools &amp; Services</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Ingersoll Rand</t>
+          <t>Incyte</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
+          <t>Biotechnology</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>PODD</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Insulet Corporation</t>
+          <t>Ingersoll Rand</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Health Care Equipment</t>
+          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>PODD</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Insulet Corporation</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Health Care Equipment</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Interactive Brokers</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Investment Banking &amp; Brokerage</t>
+          <t>Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Interactive Brokers</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6034,41 +6034,41 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Financial Exchanges &amp; Data</t>
+          <t>Investment Banking &amp; Brokerage</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Specialty Chemicals</t>
+          <t>Financial Exchanges &amp; Data</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>IP</t>
+          <t>IFF</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>International Paper</t>
+          <t>International Flavors &amp; Fragrances</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6078,327 +6078,327 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Paper &amp; Plastic Packaging Products &amp; Materials</t>
+          <t>Specialty Chemicals</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>IP</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>International Paper</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Application Software</t>
+          <t>Paper &amp; Plastic Packaging Products &amp; Materials</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Intuitive Surgical</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Health Care Equipment</t>
+          <t>Application Software</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>IVZ</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Intuitive Surgical</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Asset Management &amp; Custody Banks</t>
+          <t>Health Care Equipment</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>INVH</t>
+          <t>IVZ</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Invitation Homes</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Single-Family Residential REITs</t>
+          <t>Asset Management &amp; Custody Banks</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>INVH</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Invitation Homes</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Life Sciences Tools &amp; Services</t>
+          <t>Single-Family Residential REITs</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>IRM</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Iron Mountain</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Other Specialized REITs</t>
+          <t>Life Sciences Tools &amp; Services</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>IRM</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>J.B. Hunt</t>
+          <t>Iron Mountain</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Cargo Ground Transportation</t>
+          <t>Other Specialized REITs</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>J.B. Hunt</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Electronic Manufacturing Services</t>
+          <t>Cargo Ground Transportation</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Transaction &amp; Payment Processing Services</t>
+          <t>Electronic Manufacturing Services</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Jacobs Solutions</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Construction &amp; Engineering</t>
+          <t>Transaction &amp; Payment Processing Services</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Jacobs Solutions</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Construction &amp; Engineering</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>JCI</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Building Products</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Diversified Banks</t>
+          <t>Building Products</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>KVUE</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Kenvue</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Personal Care Products</t>
+          <t>Diversified Banks</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>KVUE</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>Kenvue</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6408,195 +6408,195 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Soft Drinks &amp; Non-alcoholic Beverages</t>
+          <t>Personal Care Products</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>KEY</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>KeyCorp</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Soft Drinks &amp; Non-alcoholic Beverages</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>KEY</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>KeyCorp</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Electronic Equipment &amp; Instruments</t>
+          <t>Regional Banks</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Household Products</t>
+          <t>Electronic Equipment &amp; Instruments</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>KIM</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Kimco Realty</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Retail REITs</t>
+          <t>Household Products</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>KMI</t>
+          <t>KIM</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Kinder Morgan</t>
+          <t>Kimco Realty</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Storage &amp; Transportation</t>
+          <t>Retail REITs</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>KMI</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>KKR &amp; Co.</t>
+          <t>Kinder Morgan</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Asset Management &amp; Custody Banks</t>
+          <t>Oil &amp; Gas Storage &amp; Transportation</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>KKR &amp; Co.</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Semiconductor Materials &amp; Equipment</t>
+          <t>Asset Management &amp; Custody Banks</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Kraft Heinz</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Packaged Foods &amp; Meats</t>
+          <t>Semiconductor Materials &amp; Equipment</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Kroger</t>
+          <t>Kraft Heinz</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -6606,95 +6606,95 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Food Retail</t>
+          <t>Packaged Foods &amp; Meats</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>LHX</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>L3Harris</t>
+          <t>Kroger</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Food Retail</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>LH</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>L3Harris</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Semiconductor Materials &amp; Equipment</t>
+          <t>Health Care Services</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Lamb Weston</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Packaged Foods &amp; Meats</t>
+          <t>Semiconductor Materials &amp; Equipment</t>
         </is>
       </c>
     </row>
@@ -6943,276 +6943,276 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>LYB</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>LyondellBasell</t>
+          <t>Lumentum</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Specialty Chemicals</t>
+          <t>Communications Equipment</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>MTB</t>
+          <t>LYB</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>LyondellBasell</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Specialty Chemicals</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>MTB</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Refining &amp; Marketing</t>
+          <t>Regional Banks</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Hotels, Resorts &amp; Cruise Lines</t>
+          <t>Oil &amp; Gas Refining &amp; Marketing</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Marsh McLennan</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Insurance Brokers</t>
+          <t>Hotels, Resorts &amp; Cruise Lines</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>MLM</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Martin Marietta Materials</t>
+          <t>Marsh McLennan</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Insurance Brokers</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>MAS</t>
+          <t>MLM</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>Martin Marietta Materials</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Building Products</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Transaction &amp; Payment Processing Services</t>
+          <t>Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>MAS</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Interactive Media &amp; Services</t>
+          <t>Building Products</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>McCormick &amp; Company</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Packaged Foods &amp; Meats</t>
+          <t>Transaction &amp; Payment Processing Services</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>McCormick &amp; Company</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Restaurants</t>
+          <t>Packaged Foods &amp; Meats</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Health Care Distributors</t>
+          <t>Restaurants</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7222,19 +7222,19 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Health Care Equipment</t>
+          <t>Health Care Distributors</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Merck &amp; Co.</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7244,129 +7244,129 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Health Care Equipment</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Merck &amp; Co.</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Interactive Media &amp; Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Life &amp; Health Insurance</t>
+          <t>Interactive Media &amp; Services</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Mettler Toledo</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Life Sciences Tools &amp; Services</t>
+          <t>Life &amp; Health Insurance</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>MGM</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>MGM Resorts</t>
+          <t>Mettler Toledo</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Casinos &amp; Gaming</t>
+          <t>Life Sciences Tools &amp; Services</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>MGM</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>MGM Resorts</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Casinos &amp; Gaming</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -7383,12 +7383,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7398,63 +7398,63 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Systems Software</t>
+          <t>Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Mid-America Apartment Communities</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Multi-Family Residential REITs</t>
+          <t>Systems Software</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Moderna</t>
+          <t>Mid-America Apartment Communities</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Multi-Family Residential REITs</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>MOH</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Moderna</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7464,19 +7464,19 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Managed Health Care</t>
+          <t>Biotechnology</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>TAP</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Molson Coors Beverage Company</t>
+          <t>Mondelez International</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7486,85 +7486,85 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Brewers</t>
+          <t>Packaged Foods &amp; Meats</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Mondelez International</t>
+          <t>Monolithic Power Systems</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Packaged Foods &amp; Meats</t>
+          <t>Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Monolithic Power Systems</t>
+          <t>Monster Beverage</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Soft Drinks &amp; Non-alcoholic Beverages</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>MCO</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Monster Beverage</t>
+          <t>Moody's Corporation</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Soft Drinks &amp; Non-alcoholic Beverages</t>
+          <t>Financial Exchanges &amp; Data</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>MCO</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Moody's Corporation</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -7574,85 +7574,85 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Financial Exchanges &amp; Data</t>
+          <t>Investment Banking &amp; Brokerage</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Mosaic Company (The)</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Investment Banking &amp; Brokerage</t>
+          <t>Fertilizers &amp; Agricultural Chemicals</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Mosaic Company (The)</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Fertilizers &amp; Agricultural Chemicals</t>
+          <t>Communications Equipment</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Communications Equipment</t>
+          <t>Financial Exchanges &amp; Data</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>MSCI Inc.</t>
+          <t>Nasdaq, Inc.</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -7669,100 +7669,100 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Nasdaq, Inc.</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Financial Exchanges &amp; Data</t>
+          <t>Technology Hardware, Storage &amp; Peripherals</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Technology Hardware, Storage &amp; Peripherals</t>
+          <t>Movies &amp; Entertainment</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Netflix</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Movies &amp; Entertainment</t>
+          <t>Gold</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>News Corp (Class A)</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Publishing</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>News Corp (Class A)</t>
+          <t>News Corp (Class B)</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -7779,100 +7779,100 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>News Corp (Class B)</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Publishing</t>
+          <t>Multi-Utilities</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>Nike, Inc.</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Multi-Utilities</t>
+          <t>Apparel, Accessories &amp; Luxury Goods</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Nike, Inc.</t>
+          <t>NiSource</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Apparel, Accessories &amp; Luxury Goods</t>
+          <t>Multi-Utilities</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>NI</t>
+          <t>NDSN</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>NiSource</t>
+          <t>Nordson Corporation</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Multi-Utilities</t>
+          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>NSC</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Nordson Corporation</t>
+          <t>Norfolk Southern</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -7882,371 +7882,371 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
+          <t>Rail Transportation</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>NSC</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Norfolk Southern</t>
+          <t>Northern Trust</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Rail Transportation</t>
+          <t>Asset Management &amp; Custody Banks</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Northern Trust</t>
+          <t>Northrop Grumman</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Asset Management &amp; Custody Banks</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>NCLH</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Northrop Grumman</t>
+          <t>Norwegian Cruise Line Holdings</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Hotels, Resorts &amp; Cruise Lines</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Norwegian Cruise Line Holdings</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Hotels, Resorts &amp; Cruise Lines</t>
+          <t>Independent Power Producers &amp; Energy Traders</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Independent Power Producers &amp; Energy Traders</t>
+          <t>Steel</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>NVR, Inc.</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Homebuilding</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>NVR</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>NVR, Inc.</t>
+          <t>NXP Semiconductors</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Homebuilding</t>
+          <t>Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>NXP Semiconductors</t>
+          <t>O'Reilly Automotive</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Automotive Retail</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>O’Reilly Automotive</t>
+          <t>Occidental Petroleum</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Automotive Retail</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Occidental Petroleum</t>
+          <t>Old Dominion</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Cargo Ground Transportation</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>OMC</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Old Dominion</t>
+          <t>Omnicom Group</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Cargo Ground Transportation</t>
+          <t>Advertising</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>OMC</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Omnicom Group</t>
+          <t>ON Semiconductor</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Advertising</t>
+          <t>Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>ON Semiconductor</t>
+          <t>Oneok</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Oil &amp; Gas Storage &amp; Transportation</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Oneok</t>
+          <t>Oracle Corporation</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Storage &amp; Transportation</t>
+          <t>Application Software</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>OTIS</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Oracle Corporation</t>
+          <t>Otis Worldwide</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Application Software</t>
+          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>OTIS</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Otis Worldwide</t>
+          <t>Paccar</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -8256,63 +8256,63 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
+          <t>Construction Machinery &amp; Heavy Transportation Equipment</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>PKG</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Paccar</t>
+          <t>Packaging Corporation of America</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Construction Machinery &amp; Heavy Transportation Equipment</t>
+          <t>Paper &amp; Plastic Packaging Products &amp; Materials</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>PKG</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Packaging Corporation of America</t>
+          <t>Palantir Technologies</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Paper &amp; Plastic Packaging Products &amp; Materials</t>
+          <t>Application Software</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Palantir Technologies</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -8322,63 +8322,63 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Application Software</t>
+          <t>Systems Software</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Paramount Skydance Corporation</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Systems Software</t>
+          <t>Movies &amp; Entertainment</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>PSKY</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Paramount Skydance Corporation</t>
+          <t>Parker Hannifin</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Movies &amp; Entertainment</t>
+          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Parker Hannifin</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -8388,41 +8388,41 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
+          <t>Human Resource &amp; Employment Services</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Human Resource &amp; Employment Services</t>
+          <t>Transaction &amp; Payment Processing Services</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>PAYC</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Paycom</t>
+          <t>Pentair</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -8432,1031 +8432,1031 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Human Resource &amp; Employment Services</t>
+          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Transaction &amp; Payment Processing Services</t>
+          <t>Soft Drinks &amp; Non-alcoholic Beverages</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Pentair</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>PCG</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>PG&amp;E Corporation</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Soft Drinks &amp; Non-alcoholic Beverages</t>
+          <t>Multi-Utilities</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Philip Morris International</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Tobacco</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>PCG</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>PG&amp;E Corporation</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Multi-Utilities</t>
+          <t>Oil &amp; Gas Refining &amp; Marketing</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>PNW</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Philip Morris International</t>
+          <t>Pinnacle West Capital</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Tobacco</t>
+          <t>Multi-Utilities</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>PNC Financial Services</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Refining &amp; Marketing</t>
+          <t>Diversified Banks</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>PNW</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Pinnacle West Capital</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Multi-Utilities</t>
+          <t>Specialty Chemicals</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>PNC Financial Services</t>
+          <t>PPL Corporation</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Diversified Banks</t>
+          <t>Electric Utilities</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Pool Corporation</t>
+          <t>Principal Financial Group</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Distributors</t>
+          <t>Life &amp; Health Insurance</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Specialty Chemicals</t>
+          <t>Personal Care Products</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>PPL Corporation</t>
+          <t>Progressive Corporation</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Electric Utilities</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Principal Financial Group</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Life &amp; Health Insurance</t>
+          <t>Industrial REITs</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Prudential Financial</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Personal Care Products</t>
+          <t>Life &amp; Health Insurance</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Progressive Corporation</t>
+          <t>Public Service Enterprise Group</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Electric Utilities</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>PTC Inc.</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Industrial REITs</t>
+          <t>Application Software</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>PSA</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Prudential Financial</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Life &amp; Health Insurance</t>
+          <t>Self-Storage REITs</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>PHM</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Public Service Enterprise Group</t>
+          <t>PulteGroup</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Electric Utilities</t>
+          <t>Homebuilding</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>PTC Inc.</t>
+          <t>Quanta Services</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Application Software</t>
+          <t>Construction &amp; Engineering</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>PSA</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Self-Storage REITs</t>
+          <t>Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>PHM</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>PulteGroup</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Homebuilding</t>
+          <t>Health Care Services</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Quanta Services</t>
+          <t>Qnity Electronics</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Construction &amp; Engineering</t>
+          <t>Semiconductor Materials &amp; Equipment</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Ralph Lauren Corporation</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Apparel, Accessories &amp; Luxury Goods</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>RJF</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>Raymond James Financial</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Investment Banking &amp; Brokerage</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Qnity Electronics</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Semiconductor Materials &amp; Equipment</t>
+          <t>Interactive Media &amp; Services</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Ralph Lauren Corporation</t>
+          <t>RTX Corporation</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Apparel, Accessories &amp; Luxury Goods</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>RJF</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Raymond James Financial</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Investment Banking &amp; Brokerage</t>
+          <t>Retail REITs</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>RTX Corporation</t>
+          <t>Regency Centers</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Retail REITs</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Regeneron Pharmaceuticals</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Retail REITs</t>
+          <t>Biotechnology</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Regency Centers</t>
+          <t>Regions Financial Corporation</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Retail REITs</t>
+          <t>Regional Banks</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals</t>
+          <t>Republic Services</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Environmental &amp; Facilities Services</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Regions Financial Corporation</t>
+          <t>ResMed|</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Health Care Equipment</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Republic Services</t>
+          <t>Revvity</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Environmental &amp; Facilities Services</t>
+          <t>Health Care Equipment</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>RMD</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>ResMed</t>
+          <t>Robinhood Markets</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Health Care Equipment</t>
+          <t>Investment Banking &amp; Brokerage</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>ROK</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Revvity</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Health Care Equipment</t>
+          <t>Electrical Components &amp; Equipment</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>ROL</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Robinhood Markets</t>
+          <t>Rollins, Inc.</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Investment Banking &amp; Brokerage</t>
+          <t>Environmental &amp; Facilities Services</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>ROK</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Rockwell Automation</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Electrical Components &amp; Equipment</t>
+          <t>Electronic Equipment &amp; Instruments</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>ROL</t>
+          <t>ROST</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Rollins, Inc.</t>
+          <t>Ross Stores</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Environmental &amp; Facilities Services</t>
+          <t>Apparel Retail</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Electronic Equipment &amp; Instruments</t>
+          <t>Hotels, Resorts &amp; Cruise Lines</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Ross Stores</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Apparel Retail</t>
+          <t>Financial Exchanges &amp; Data</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Hotels, Resorts &amp; Cruise Lines</t>
+          <t>Application Software</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Sandisk</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Financial Exchanges &amp; Data</t>
+          <t>Technology Hardware, Storage &amp; Peripherals</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>SBAC</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Application Software</t>
+          <t>Telecom Tower REITs</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Sandisk</t>
+          <t>Schlumberger</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Technology Hardware, Storage &amp; Peripherals</t>
+          <t>Oil &amp; Gas Equipment &amp; Services</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>SBAC</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Seagate Technology</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Telecom Tower REITs</t>
+          <t>Technology Hardware, Storage &amp; Peripherals</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>SRE</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Schlumberger</t>
+          <t>Sempra</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Equipment &amp; Services</t>
+          <t>Multi-Utilities</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Seagate Technology</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -9466,393 +9466,393 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Technology Hardware, Storage &amp; Peripherals</t>
+          <t>Systems Software</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>SRE</t>
+          <t>SHW</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Sempra</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Multi-Utilities</t>
+          <t>Specialty Chemicals</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>SPG</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Simon Property Group</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Systems Software</t>
+          <t>Retail REITs</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>SHW</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Specialty Chemicals</t>
+          <t>Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>SPG</t>
+          <t>SJM</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Simon Property Group</t>
+          <t>J.M. Smucker Company (The)</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Retail REITs</t>
+          <t>Packaged Foods &amp; Meats</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>SW</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>Smurfit Westrock</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Paper &amp; Plastic Packaging Products &amp; Materials</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>SJM</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>J.M. Smucker Company (The)</t>
+          <t>Snap-on</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Packaged Foods &amp; Meats</t>
+          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Smurfit Westrock</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Paper &amp; Plastic Packaging Products &amp; Materials</t>
+          <t>Health Care Technology</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>SO</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Snap-on</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
+          <t>Electric Utilities</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>LUV</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Southwest Airlines</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Health Care Technology</t>
+          <t>Passenger Airlines</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Stanley Black &amp; Decker</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Electric Utilities</t>
+          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>LUV</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Southwest Airlines</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Passenger Airlines</t>
+          <t>Restaurants</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker</t>
+          <t>State Street Corporation</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
+          <t>Asset Management &amp; Custody Banks</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Steel Dynamics</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Restaurants</t>
+          <t>Steel</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>STT</t>
+          <t>STE</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>State Street Corporation</t>
+          <t>Steris</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Asset Management &amp; Custody Banks</t>
+          <t>Health Care Equipment</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>SYK</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Steel Dynamics</t>
+          <t>Stryker Corporation</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Health Care Equipment</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>STE</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Steris</t>
+          <t>Supermicro</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Health Care Equipment</t>
+          <t>Technology Hardware, Storage &amp; Peripherals</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>SYK</t>
+          <t>SYF</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Stryker Corporation</t>
+          <t>Synchrony Financial</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Health Care Equipment</t>
+          <t>Consumer Finance</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Supermicro</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -9862,85 +9862,85 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Technology Hardware, Storage &amp; Peripherals</t>
+          <t>Application Software</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>SYY</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Synchrony Financial</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Consumer Finance</t>
+          <t>Food Distributors</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>T-Mobile US</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Application Software</t>
+          <t>Wireless Telecommunication Services</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Food Distributors</t>
+          <t>Asset Management &amp; Custody Banks</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>TTWO</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>T-Mobile US</t>
+          <t>Take-Two Interactive</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -9950,129 +9950,129 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Wireless Telecommunication Services</t>
+          <t>Interactive Home Entertainment</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>TPR</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Tapestry, Inc.</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Asset Management &amp; Custody Banks</t>
+          <t>Apparel, Accessories &amp; Luxury Goods</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>TTWO</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Take-Two Interactive</t>
+          <t>Targa Resources</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Interactive Home Entertainment</t>
+          <t>Oil &amp; Gas Storage &amp; Transportation</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>TPR</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Tapestry, Inc.</t>
+          <t>Target Corporation</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Apparel, Accessories &amp; Luxury Goods</t>
+          <t>Consumer Staples Merchandise Retail</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>TEL</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Targa Resources</t>
+          <t>TE Connectivity</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Storage &amp; Transportation</t>
+          <t>Electronic Manufacturing Services</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>TDY</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Target Corporation</t>
+          <t>Teledyne Technologies</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Consumer Staples Merchandise Retail</t>
+          <t>Electronic Equipment &amp; Instruments</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>TEL</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>TE Connectivity</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -10082,41 +10082,41 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Electronic Manufacturing Services</t>
+          <t>Semiconductor Materials &amp; Equipment</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>TDY</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Teledyne Technologies</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Electronic Equipment &amp; Instruments</t>
+          <t>Automobile Manufacturers</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -10126,129 +10126,129 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Semiconductor Materials &amp; Equipment</t>
+          <t>Semiconductors</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Texas Pacific Land Corporation</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Automobile Manufacturers</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>TPL</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Texas Pacific Land Corporation</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Life Sciences Tools &amp; Services</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Textron</t>
+          <t>TJX Companies</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Apparel Retail</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>TKO Group Holdings</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Life Sciences Tools &amp; Services</t>
+          <t>Movies &amp; Entertainment</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>TSCO</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>TJX Companies</t>
+          <t>Tractor Supply</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -10258,173 +10258,173 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Apparel Retail</t>
+          <t>Other Specialty Retail</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>TKO Group Holdings</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Movies &amp; Entertainment</t>
+          <t>Building Products</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>TTD</t>
+          <t>TDG</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Trade Desk (The)</t>
+          <t>TransDigm Group</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Advertising</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>TSCO</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Tractor Supply</t>
+          <t>Travelers Companies (The)</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Other Specialty Retail</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Trimble Inc.</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Building Products</t>
+          <t>Application Software</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>TDG</t>
+          <t>TFC</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>TransDigm Group</t>
+          <t>Truist Financial</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Diversified Banks</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Travelers Companies (The)</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Application Software</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>TSN</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Trimble Inc.</t>
+          <t>Tyson Foods</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Electronic Equipment &amp; Instruments</t>
+          <t>Packaged Foods &amp; Meats</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>TFC</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Truist Financial</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -10441,78 +10441,78 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Application Software</t>
+          <t>Passenger Ground Transportation</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>TSN</t>
+          <t>UDR</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Tyson Foods</t>
+          <t>UDR, Inc.</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Packaged Foods &amp; Meats</t>
+          <t>Multi-Family Residential REITs</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Ulta Beauty</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Diversified Banks</t>
+          <t>Other Specialty Retail</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -10522,63 +10522,63 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Passenger Ground Transportation</t>
+          <t>Rail Transportation</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>UDR</t>
+          <t>UAL</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>UDR, Inc.</t>
+          <t>United Airlines Holdings</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Multi-Family Residential REITs</t>
+          <t>Passenger Airlines</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Ulta Beauty</t>
+          <t>United Parcel Service</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Other Specialty Retail</t>
+          <t>Air Freight &amp; Logistics</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>URI</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>United Rentals</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -10588,85 +10588,85 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Rail Transportation</t>
+          <t>Trading Companies &amp; Distributors</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>UAL</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>United Airlines Holdings</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Passenger Airlines</t>
+          <t>Managed Health Care</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>United Parcel Service</t>
+          <t>Universal Health Services</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Air Freight &amp; Logistics</t>
+          <t>Health Care Facilities</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>URI</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>United Rentals</t>
+          <t>Valero Energy</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Trading Companies &amp; Distributors</t>
+          <t>Oil &amp; Gas Refining &amp; Marketing</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Veeva Systems</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -10676,85 +10676,85 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Managed Health Care</t>
+          <t>Health Care Technology</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>VTR</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Universal Health Services</t>
+          <t>Ventas</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Health Care Facilities</t>
+          <t>Health Care REITs</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>VLTO</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Valero Energy</t>
+          <t>Veralto</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Refining &amp; Marketing</t>
+          <t>Environmental &amp; Facilities Services</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>VTR</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Ventas</t>
+          <t>Verisign</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Health Care REITs</t>
+          <t>Internet Services &amp; Infrastructure</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>VLTO</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Veralto</t>
+          <t>Verisk Analytics</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -10764,85 +10764,85 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Environmental &amp; Facilities Services</t>
+          <t>Research &amp; Consulting Services</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Verisign</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Internet Services &amp; Infrastructure</t>
+          <t>Integrated Telecommunication Services</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>VRTX</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Verisk Analytics</t>
+          <t>Vertex Pharmaceuticals</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Research &amp; Consulting Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Integrated Telecommunication Services</t>
+          <t>Electrical Components &amp; Equipment</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>VRTX</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals</t>
+          <t>Viatris</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -10852,95 +10852,95 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>VICI</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Viatris</t>
+          <t>Vici Properties</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Hotel &amp; Resort REITs</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>VICI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Vici Properties</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Hotel &amp; Resort REITs</t>
+          <t>Transaction &amp; Payment Processing Services</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Vistra Corp.</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Transaction &amp; Payment Processing Services</t>
+          <t>Electric Utilities</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>VMRK</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Vistra Corp.</t>
+          <t>Vivmark Residential</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Electric Utilities</t>
+          <t>Multi-Family Residential REITs</t>
         </is>
       </c>
     </row>
